--- a/quotes/PR-217-228/Rates_Needed_PR217_PR228.xlsx
+++ b/quotes/PR-217-228/Rates_Needed_PR217_PR228.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="190">
   <si>
     <t xml:space="preserve">Rates Needed - PR-217 &amp; PR-228 (unverified items, highest value first)</t>
   </si>
@@ -88,49 +88,49 @@
     <t xml:space="preserve">Spec farq</t>
   </si>
   <si>
+    <t xml:space="preserve">CORDLESS IMPACT WRENCH 350N (Bosch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS WELDING RODS 309L-16 2.6MM NO.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENCH VISE 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yato (heavy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS TOOL 16MMX16MMX200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHANICAL JACK 5 TON (Japan or Germany)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masada (Japan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS WELDING RODS 316L-16 2.6MM NO.12</t>
+  </si>
+  <si>
     <t xml:space="preserve">AC/DC SINGLE PHASE WELDING PLANT 300 AMP</t>
   </si>
   <si>
-    <t xml:space="preserve">Industrial (AC/DC TIG 300A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDLESS IMPACT WRENCH 350N (Bosch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS WELDING RODS 309L-16 2.6MM NO.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BENCH VISE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato (heavy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 16MMX16MMX200MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL JACK 5 TON (Japan or Germany)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masada (Japan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS WELDING RODS 316L-16 2.6MM NO.12</t>
+    <t xml:space="preserve">WACTA20</t>
   </si>
   <si>
     <t xml:space="preserve">DRILL BIT 08 MM (Yato or any Good brand taiwan)</t>
@@ -139,27 +139,15 @@
     <t xml:space="preserve">Dormer A002</t>
   </si>
   <si>
-    <t xml:space="preserve">BENCH VISE 08"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato YT-65049</t>
-  </si>
-  <si>
     <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
   </si>
   <si>
     <t xml:space="preserve">HSS TOOL 12MMX12MMX200MM</t>
   </si>
   <si>
-    <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
-  </si>
-  <si>
     <t xml:space="preserve">MECHANICAL JACK 03 TONS (Japan or germany)</t>
   </si>
   <si>
-    <t xml:space="preserve">DOUBLE OPEN END WRENCH 6 TO 32 (12 PCS SET)</t>
-  </si>
-  <si>
     <t xml:space="preserve">HSS PARTING OFF TOOL 1/8" X 3/4" X 8"</t>
   </si>
   <si>
@@ -172,9 +160,6 @@
     <t xml:space="preserve">HSS TOOL 10MMX10MMX200MM</t>
   </si>
   <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 36"</t>
-  </si>
-  <si>
     <t xml:space="preserve">HSS DRILL BIT 35MM TAPER SHANK</t>
   </si>
   <si>
@@ -184,481 +169,421 @@
     <t xml:space="preserve">DRILL BIT 4MM</t>
   </si>
   <si>
+    <t xml:space="preserve">HSS TOOL 08X08X200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 16MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer C-series HSS-Co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 2.5MM E6013, NO 10 Zodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 32MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 8MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAK 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCUMFERENCE TAPE (60-950) (D20-300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 10MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 2.5MM E7018 NO-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortrex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 6MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 18MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 5MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERNAL EXTRACTOR WITH REINFORCED COLLAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 19MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCUMFERENCE TAPE (940-2200) (D300-700)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIG WELDING TORCH AIR-COOLED 5METER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COTTON ROPE 2MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 17.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL GREASE GUN 5KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVOLVING CENTRE MT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertex (Taiwan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C-CLAMP 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1-1/4" BSPF LEFT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 17MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 25MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 16.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 25MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 16MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 JAW CHUCK 4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRASS PLATED CUP WIRE BRUSH 125MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 15.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVOLVING CENTRE MT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 22MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 15MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR BOLT 12X160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUT PIECES OF CLOTHS FOR CLEANING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1-1/4" BSPF RIGHT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 14MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRINDER WHEEL SILICON CARBIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1/4" BSPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
     <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
   </si>
   <si>
-    <t xml:space="preserve">HSS TOOL 08X08X200MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer C-series HSS-Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 2.5MM E6013, NO 10 Zodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 32MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A095 (HSS-Co)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 8MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAK 250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCUMFERENCE TAPE (60-950) (D20-300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 10MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 2.5MM E7018 NO-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortrex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 6MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 18MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 12MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 5MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERNAL EXTRACTOR WITH REINFORCED COLLAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 19MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCUMFERENCE TAPE (940-2200) (D300-700)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIG WELDING TORCH AIR-COOLED 5METER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTTON ROPE 2MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 200X200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 17.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUAL GREASE GUN 5KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVOLVING CENTRE MT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertex (Taiwan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-CLAMP 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1-1/4" BSPF LEFT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 17MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 25MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 16.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 25MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 16MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 24"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 JAW CHUCK 4"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRASS PLATED CUP WIRE BRUSH 125MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 15.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVOLVING CENTRE MT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 22MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 15MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLEDGE HAMMER 3 LBS WITH FIBREGLASS HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANCHOR BOLT 12X160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 250X250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUT PIECES OF CLOTHS FOR CLEANING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1-1/4" BSPF RIGHT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 14MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
+    <t xml:space="preserve">Harden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1/8" BSPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUEL GAS REGULATOR 0-2.5 BAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1" BSPF RIGHT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED OXIDE POWDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGNET SPIRIT LEVEL 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREASE PIPE 1/4"X12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUFFING DISC 125MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET M16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUNGSTEN ELECTRODE 2.4MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR GREASE GUN 500CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICE GRIP PLIER 08"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1/2" BSPF RIGHT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSIDE CALIPER 20"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic (Taiwan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTSIDE CALIPER 20"</t>
   </si>
   <si>
     <t xml:space="preserve">STEEL MEASURMENT TAPE 100M</t>
   </si>
   <si>
-    <t xml:space="preserve">GAS CUTTING TORCH MEDIUM 6-50MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harris type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL SILICON CARBIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/4" BSPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFT FACE DEAD BLOW HAMMER 50MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET M20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALIGNING PRY BAR DIA 5/8" X 18" LENGTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR BOLT 10X110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RACHET TAP HANDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 300MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 3/8" BSPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET M18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STONE CUTTING DISC 4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhodius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUNDE FILE 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORCH HEAD ARGON WELDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OXYGEN HOSE 08MM ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACETYLENE GAS HOSE 08 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP HANDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
   </si>
   <si>
     <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
   </si>
   <si>
-    <t xml:space="preserve">TAP SET 1/8" BSPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUEL GAS REGULATOR 0-2.5 BAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1" BSPF RIGHT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 10"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-CLAMP 6"</t>
+    <t xml:space="preserve">COLLECT BODY FOR ARGON 2.4MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRAULIC JACK 3 TON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHORT SLEEVE TIG WELDING GLOVES 10-INCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSIDE CALIPER 06"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTSIDE CALIPER 06"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING ELCTRODE HOLDER 1000 AMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLLECT OF ARGON 2.4MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING HELMET (FLIP FRONT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARGON GAS HOSE 06MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIP CLEANER FOR GAS WELDING TORCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN HEX KEY 12MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT SIZE 16MM</t>
   </si>
   <si>
     <t xml:space="preserve">CABLE LUGS 1000 AMPERE</t>
   </si>
   <si>
-    <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 300MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RED OXIDE POWDER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEEL MEASURMENT TAPE 50M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGNET SPIRIT LEVEL 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANCHOR BOLT 10X110</t>
+    <t xml:space="preserve">GAS HOSE CONNECTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOILET CLEANING BRUSH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEEDLE FILE (5PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT SIZE 12MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT HANDLE LARGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 150MM</t>
   </si>
   <si>
     <t xml:space="preserve">BLIND RIVETS 04MMX25MM (1000PCS)</t>
   </si>
   <si>
-    <t xml:space="preserve">Generic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GREASE PIPE 1/4"X12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUFFING DISC 125MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLATE METAL SCRAPPER 50MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUNGSTEN ELECTRODE 2.4MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIR GREASE GUN 500CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPIRIT LEVEL 1 METER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADJUSTABLE WRENCH 15"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VICE GRIP PLIER 08"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALIGNING PRY BAR DIA 5/8" X 18" LENGTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/2" BSPF RIGHT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSIDE CALIPER 20"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic (Taiwan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OUTSIDE CALIPER 20"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RACHET TAP HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 3/8" BSPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STONE CUTTING DISC 4"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 150MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUNDE FILE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDRAULIC JACK 5 TON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato YT-17002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORCH HEAD ARGON WELDING</t>
+    <t xml:space="preserve">CERAMIC CUP NO.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERAMIC CUP NO.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERAMIC CUP NO.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT SIZE 10MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT HANDLE MEDIUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT SIZE 8MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT SIZE 6MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT HANDLE SMALL</t>
   </si>
   <si>
     <t xml:space="preserve">EARTH CLAMP 1000 AMP</t>
   </si>
   <si>
-    <t xml:space="preserve">OXYGEN HOSE 08MM ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACETYLENE GAS HOSE 08 ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIRE BRUSH HEAVY DUTY 4/5 NROW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLLECT BODY FOR ARGON 2.4MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDRAULIC JACK 3 TON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato YT-17001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHORT SLEEVE TIG WELDING GLOVES 10-INCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSIDE CALIPER 06"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OUTSIDE CALIPER 06"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING ELCTRODE HOLDER 1000 AMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLLECT OF ARGON 2.4MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUTTING TIPS/NOZZLES NO. 03 (12MM-25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING HELMET (FLIP FRONT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARGON GAS HOSE 06MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEEDLE FILE (5PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIP CLEANER FOR GAS WELDING TORCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN HEX KEY 12MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUTTING TIPS/NOZZLES NO. 02 (6MM-12MM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT SIZE 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAS HOSE CONNECTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOILET CLEANING BRUSH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT SIZE 12MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT HANDLE LARGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERAMIC CUP NO.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERAMIC CUP NO.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERAMIC CUP NO.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT SIZE 10MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT HANDLE MEDIUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT SIZE 8MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT SIZE 6MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT HANDLE SMALL</t>
-  </si>
-  <si>
     <t xml:space="preserve">CYLINDER KEY/SPANNER</t>
   </si>
   <si>
     <t xml:space="preserve">DIE NUT SIZE 5MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEASURING TAPE 5M</t>
   </si>
   <si>
     <t xml:space="preserve">STEEL NAIL 1-1/2" Taiwan</t>
@@ -1108,7 +1033,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I176"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1242,19 +1167,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>330000</v>
+        <v>300000</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="8"/>
@@ -1267,19 +1192,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>300000</v>
+        <v>240000</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
@@ -1292,19 +1217,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>167</v>
+        <v>224</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>240000</v>
+        <v>220000</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="8"/>
@@ -1317,19 +1242,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>220000</v>
+        <v>192000</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
@@ -1342,19 +1267,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>228</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>192000</v>
+        <v>150000</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="8"/>
@@ -1367,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>32</v>
@@ -1379,7 +1304,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="8"/>
@@ -1392,19 +1317,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>140000</v>
+        <v>136000</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="8"/>
@@ -1417,24 +1342,24 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="F14" s="6" t="n">
-        <v>136000</v>
+        <v>126000</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="8"/>
       <c r="I14" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1467,24 +1392,24 @@
         <v>12</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>223</v>
+        <v>9</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>120000</v>
+        <v>118400</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="8"/>
       <c r="I16" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1492,24 +1417,24 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>9</v>
+        <v>227</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>118400</v>
+        <v>115200</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="8"/>
       <c r="I17" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1517,19 +1442,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>227</v>
+        <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>115200</v>
+        <v>110000</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="8"/>
@@ -1542,19 +1467,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>13</v>
+        <v>229</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>112000</v>
+        <v>108000</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="8"/>
@@ -1567,24 +1492,24 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>5</v>
+        <v>165</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="F20" s="6" t="n">
-        <v>110000</v>
+        <v>89920</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="8"/>
       <c r="I20" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1592,19 +1517,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>108000</v>
+        <v>86400</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -1617,19 +1542,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>108000</v>
+        <v>68210</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="8"/>
@@ -1642,24 +1567,24 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>89920</v>
+        <v>65000</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="8"/>
       <c r="I23" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1667,7 +1592,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>49</v>
@@ -1676,10 +1601,10 @@
         <v>24</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>86400</v>
+        <v>62400</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
@@ -1692,19 +1617,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>72000</v>
+        <v>60000</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="8"/>
@@ -1717,19 +1642,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>87</v>
+        <v>209</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>68210</v>
+        <v>59970</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="8"/>
@@ -1742,24 +1667,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>240</v>
+        <v>164</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>65000</v>
+        <v>58000</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="8"/>
       <c r="I27" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1767,19 +1692,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>64000</v>
+        <v>57270</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
@@ -1792,19 +1717,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>62400</v>
+        <v>54060</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="8"/>
@@ -1817,19 +1742,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>56</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>60000</v>
+        <v>52000</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="8"/>
@@ -1842,19 +1767,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>209</v>
+        <v>69</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>59970</v>
+        <v>50000</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="8"/>
@@ -1867,24 +1792,24 @@
         <v>28</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>59</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>58000</v>
+        <v>49980</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="8"/>
       <c r="I32" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1892,19 +1817,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>86</v>
+        <v>207</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>60</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>57270</v>
+        <v>46560</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="8"/>
@@ -1917,24 +1842,24 @@
         <v>30</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>62</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>55000</v>
+        <v>46500</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
       <c r="I34" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1942,7 +1867,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>63</v>
@@ -1951,10 +1876,10 @@
         <v>6</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>54060</v>
+        <v>46500</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="8"/>
@@ -1967,7 +1892,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>64</v>
@@ -1976,10 +1901,10 @@
         <v>2</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>52000</v>
+        <v>45780</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -1992,19 +1917,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>69</v>
+        <v>204</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>50000</v>
+        <v>42780</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -2017,19 +1942,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>49980</v>
+        <v>42000</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
@@ -2042,19 +1967,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>46560</v>
+        <v>41980</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
@@ -2067,24 +1992,24 @@
         <v>36</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>46500</v>
+        <v>40000</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2092,19 +2017,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>205</v>
+        <v>70</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>46500</v>
+        <v>40000</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
@@ -2117,10 +2042,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>210</v>
+        <v>96</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>2</v>
@@ -2129,7 +2054,7 @@
         <v>58</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>45780</v>
+        <v>40000</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
@@ -2142,19 +2067,19 @@
         <v>39</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>208</v>
+        <v>123</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>43080</v>
+        <v>40000</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
@@ -2167,19 +2092,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>6</v>
+        <v>500</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>42780</v>
+        <v>40000</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
@@ -2192,19 +2117,19 @@
         <v>41</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>42000</v>
+        <v>37020</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
@@ -2217,19 +2142,19 @@
         <v>42</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>41980</v>
+        <v>36000</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="8"/>
@@ -2242,19 +2167,19 @@
         <v>43</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>77</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>40000</v>
+        <v>36000</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="8"/>
@@ -2267,19 +2192,19 @@
         <v>44</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>40000</v>
+        <v>36000</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="8"/>
@@ -2292,19 +2217,19 @@
         <v>45</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>40000</v>
+        <v>36000</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="8"/>
@@ -2317,19 +2242,19 @@
         <v>46</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>40000</v>
+        <v>35360</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="8"/>
@@ -2342,19 +2267,19 @@
         <v>47</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>40000</v>
+        <v>34430</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="8"/>
@@ -2367,7 +2292,7 @@
         <v>48</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>83</v>
@@ -2376,10 +2301,10 @@
         <v>2</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>38000</v>
+        <v>33720</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="8"/>
@@ -2392,19 +2317,19 @@
         <v>49</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>84</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>37020</v>
+        <v>33400</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="8"/>
@@ -2417,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>85</v>
@@ -2426,10 +2351,10 @@
         <v>2</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>36000</v>
+        <v>32060</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="8"/>
@@ -2442,19 +2367,19 @@
         <v>51</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>66</v>
+        <v>222</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>36000</v>
+        <v>32000</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="8"/>
@@ -2467,19 +2392,19 @@
         <v>52</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>36000</v>
+        <v>31200</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="8"/>
@@ -2492,19 +2417,19 @@
         <v>53</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>36000</v>
+        <v>30420</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="8"/>
@@ -2517,19 +2442,19 @@
         <v>54</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>35360</v>
+        <v>30000</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="8"/>
@@ -2542,19 +2467,19 @@
         <v>55</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>34430</v>
+        <v>30000</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="8"/>
@@ -2567,19 +2492,19 @@
         <v>56</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>33720</v>
+        <v>28830</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="8"/>
@@ -2592,19 +2517,19 @@
         <v>57</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>212</v>
+        <v>76</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>33400</v>
+        <v>28760</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="8"/>
@@ -2617,19 +2542,19 @@
         <v>58</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>32060</v>
+        <v>28500</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="8"/>
@@ -2642,19 +2567,19 @@
         <v>59</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>34</v>
+        <v>159</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>32000</v>
+        <v>28000</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="8"/>
@@ -2667,19 +2592,19 @@
         <v>60</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>32000</v>
+        <v>26000</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="8"/>
@@ -2692,19 +2617,19 @@
         <v>61</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>31200</v>
+        <v>26000</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="8"/>
@@ -2717,19 +2642,19 @@
         <v>62</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>30420</v>
+        <v>25460</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="8"/>
@@ -2742,19 +2667,19 @@
         <v>63</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="8"/>
@@ -2767,19 +2692,19 @@
         <v>64</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="8"/>
@@ -2792,19 +2717,19 @@
         <v>65</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>28830</v>
+        <v>22500</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="8"/>
@@ -2817,24 +2742,24 @@
         <v>66</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C70" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D70" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="F70" s="6" t="n">
-        <v>28760</v>
+        <v>22185</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="8"/>
       <c r="I70" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2842,19 +2767,19 @@
         <v>67</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>104</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>28500</v>
+        <v>21600</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="8"/>
@@ -2867,19 +2792,19 @@
         <v>68</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>28500</v>
+        <v>21000</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="8"/>
@@ -2892,19 +2817,19 @@
         <v>69</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>106</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>28000</v>
+        <v>21000</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="8"/>
@@ -2917,19 +2842,19 @@
         <v>70</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>107</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>28000</v>
+        <v>21000</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="8"/>
@@ -2942,19 +2867,19 @@
         <v>71</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>108</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>26000</v>
+        <v>19200</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="8"/>
@@ -2967,24 +2892,24 @@
         <v>72</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>109</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>26000</v>
+        <v>18796</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="8"/>
       <c r="I76" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2992,19 +2917,19 @@
         <v>73</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>25460</v>
+        <v>18000</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="8"/>
@@ -3017,19 +2942,19 @@
         <v>74</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="8"/>
@@ -3042,19 +2967,19 @@
         <v>75</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
@@ -3067,19 +2992,19 @@
         <v>76</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
@@ -3092,19 +3017,19 @@
         <v>77</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>115</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
@@ -3117,19 +3042,19 @@
         <v>78</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>22500</v>
+        <v>15600</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="8"/>
@@ -3142,19 +3067,19 @@
         <v>79</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>21600</v>
+        <v>15000</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="8"/>
@@ -3167,10 +3092,10 @@
         <v>80</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>3</v>
@@ -3179,7 +3104,7 @@
         <v>4</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>21000</v>
+        <v>14400</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="8"/>
@@ -3192,19 +3117,19 @@
         <v>81</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>21000</v>
+        <v>14400</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="8"/>
@@ -3217,19 +3142,19 @@
         <v>82</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>21000</v>
+        <v>14400</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="8"/>
@@ -3242,19 +3167,19 @@
         <v>83</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="8"/>
@@ -3267,19 +3192,19 @@
         <v>84</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>20400</v>
+        <v>13200</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="8"/>
@@ -3292,19 +3217,19 @@
         <v>85</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>19200</v>
+        <v>13000</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="8"/>
@@ -3317,19 +3242,19 @@
         <v>86</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>18900</v>
+        <v>13000</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -3342,19 +3267,19 @@
         <v>87</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D91" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>18000</v>
+        <v>12900</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -3367,24 +3292,24 @@
         <v>88</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
       <c r="I92" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3392,19 +3317,19 @@
         <v>89</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D93" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>18000</v>
+        <v>11000</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
@@ -3417,19 +3342,19 @@
         <v>90</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>31</v>
+        <v>193</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>17400</v>
+        <v>11000</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="8"/>
@@ -3442,19 +3367,19 @@
         <v>91</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>106</v>
+        <v>195</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>16800</v>
+        <v>11000</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="8"/>
@@ -3467,24 +3392,24 @@
         <v>92</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>237</v>
+        <v>60</v>
       </c>
       <c r="C96" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D96" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="F96" s="6" t="n">
-        <v>16800</v>
+        <v>10500</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="8"/>
       <c r="I96" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3492,7 +3417,7 @@
         <v>93</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>132</v>
@@ -3501,10 +3426,10 @@
         <v>3</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>16500</v>
+        <v>10500</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="8"/>
@@ -3517,19 +3442,19 @@
         <v>94</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>133</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>16000</v>
+        <v>10500</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="8"/>
@@ -3542,24 +3467,24 @@
         <v>95</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>134</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>16000</v>
+        <v>10497</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="8"/>
       <c r="I99" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3567,19 +3492,19 @@
         <v>96</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>154</v>
+        <v>88</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>15600</v>
+        <v>10000</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="8"/>
@@ -3592,24 +3517,24 @@
         <v>97</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="C101" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="E101" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D101" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>86</v>
-      </c>
       <c r="F101" s="6" t="n">
-        <v>15000</v>
+        <v>9750</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="8"/>
       <c r="I101" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3617,19 +3542,19 @@
         <v>98</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>137</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>15000</v>
+        <v>9600</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="8"/>
@@ -3642,24 +3567,24 @@
         <v>99</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>138</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>15000</v>
+        <v>9375</v>
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="8"/>
       <c r="I103" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3667,19 +3592,19 @@
         <v>100</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>139</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>15000</v>
+        <v>9000</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="8"/>
@@ -3692,19 +3617,19 @@
         <v>101</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>14400</v>
+        <v>8800</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="8"/>
@@ -3717,19 +3642,19 @@
         <v>102</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>58</v>
+        <v>184</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>14400</v>
+        <v>8700</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="8"/>
@@ -3742,24 +3667,24 @@
         <v>103</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="C107" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E107" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D107" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="F107" s="6" t="n">
-        <v>14400</v>
+        <v>8400</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="8"/>
       <c r="I107" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3767,19 +3692,19 @@
         <v>104</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>144</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>14400</v>
+        <v>8000</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="8"/>
@@ -3792,7 +3717,7 @@
         <v>105</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>187</v>
+        <v>92</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>145</v>
@@ -3801,10 +3726,10 @@
         <v>2</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="8"/>
@@ -3817,19 +3742,19 @@
         <v>106</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>146</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>13200</v>
+        <v>7500</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="8"/>
@@ -3842,19 +3767,19 @@
         <v>107</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>147</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>13000</v>
+        <v>7000</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="8"/>
@@ -3867,19 +3792,19 @@
         <v>108</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D112" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>13000</v>
+        <v>7000</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="8"/>
@@ -3892,19 +3817,19 @@
         <v>109</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>12900</v>
+        <v>6750</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="8"/>
@@ -3917,19 +3842,19 @@
         <v>110</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>12600</v>
+        <v>6750</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="8"/>
@@ -3942,19 +3867,19 @@
         <v>111</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>12500</v>
+        <v>6400</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="8"/>
@@ -3967,24 +3892,24 @@
         <v>112</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>39</v>
+        <v>191</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>12000</v>
+        <v>6400</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="8"/>
       <c r="I116" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3992,10 +3917,10 @@
         <v>113</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>3</v>
@@ -4004,7 +3929,7 @@
         <v>4</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="8"/>
@@ -4017,24 +3942,24 @@
         <v>114</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="8"/>
       <c r="I118" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4042,19 +3967,19 @@
         <v>115</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="8"/>
@@ -4067,24 +3992,24 @@
         <v>116</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>156</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>11000</v>
+        <v>5950</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="8"/>
       <c r="I120" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4092,19 +4017,19 @@
         <v>117</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>10500</v>
+        <v>5400</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="8"/>
@@ -4117,19 +4042,19 @@
         <v>118</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>10500</v>
+        <v>5400</v>
       </c>
       <c r="G122" s="7"/>
       <c r="H122" s="8"/>
@@ -4142,19 +4067,19 @@
         <v>119</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>10000</v>
+        <v>5400</v>
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="8"/>
@@ -4167,24 +4092,24 @@
         <v>120</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>9600</v>
+        <v>5220</v>
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="8"/>
       <c r="I124" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4192,19 +4117,19 @@
         <v>121</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>9000</v>
+        <v>4800</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="8"/>
@@ -4217,19 +4142,19 @@
         <v>122</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>188</v>
+        <v>125</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>8800</v>
+        <v>4800</v>
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="8"/>
@@ -4242,19 +4167,19 @@
         <v>123</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>8700</v>
+        <v>4400</v>
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="8"/>
@@ -4267,19 +4192,19 @@
         <v>124</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>164</v>
+        <v>25</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>8400</v>
+        <v>4000</v>
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="8"/>
@@ -4292,19 +4217,19 @@
         <v>125</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>165</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>8400</v>
+        <v>4000</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="8"/>
@@ -4317,19 +4242,19 @@
         <v>126</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>8000</v>
+        <v>3900</v>
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="8"/>
@@ -4342,19 +4267,19 @@
         <v>127</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>8000</v>
+        <v>3750</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="8"/>
@@ -4367,19 +4292,19 @@
         <v>128</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>7500</v>
+        <v>3600</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="8"/>
@@ -4392,24 +4317,24 @@
         <v>129</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>169</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>7500</v>
+        <v>3600</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="8"/>
       <c r="I133" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4417,19 +4342,19 @@
         <v>130</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="8"/>
@@ -4442,19 +4367,19 @@
         <v>131</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="G135" s="7"/>
       <c r="H135" s="8"/>
@@ -4467,24 +4392,24 @@
         <v>132</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="F136" s="6" t="n">
-        <v>6900</v>
+        <v>2704</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="8"/>
       <c r="I136" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4492,19 +4417,19 @@
         <v>133</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>117</v>
+        <v>217</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>6750</v>
+        <v>2600</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="8"/>
@@ -4517,19 +4442,19 @@
         <v>134</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>118</v>
+        <v>221</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>6750</v>
+        <v>2600</v>
       </c>
       <c r="G138" s="7"/>
       <c r="H138" s="8"/>
@@ -4542,24 +4467,24 @@
         <v>135</v>
       </c>
       <c r="B139" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C139" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D139" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="F139" s="6" t="n">
-        <v>6600</v>
+        <v>2580</v>
       </c>
       <c r="G139" s="7"/>
       <c r="H139" s="8"/>
       <c r="I139" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4567,24 +4492,24 @@
         <v>136</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>6400</v>
+        <v>2382</v>
       </c>
       <c r="G140" s="7"/>
       <c r="H140" s="8"/>
       <c r="I140" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4592,19 +4517,19 @@
         <v>137</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>6400</v>
+        <v>2100</v>
       </c>
       <c r="G141" s="7"/>
       <c r="H141" s="8"/>
@@ -4617,19 +4542,19 @@
         <v>138</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F142" s="6" t="n">
-        <v>6000</v>
+        <v>2100</v>
       </c>
       <c r="G142" s="7"/>
       <c r="H142" s="8"/>
@@ -4642,19 +4567,19 @@
         <v>139</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>6000</v>
+        <v>2100</v>
       </c>
       <c r="G143" s="7"/>
       <c r="H143" s="8"/>
@@ -4667,19 +4592,19 @@
         <v>140</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>6000</v>
+        <v>2100</v>
       </c>
       <c r="G144" s="7"/>
       <c r="H144" s="8"/>
@@ -4692,19 +4617,19 @@
         <v>141</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>5400</v>
+        <v>1900</v>
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="8"/>
@@ -4717,19 +4642,19 @@
         <v>142</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="F146" s="6" t="n">
-        <v>5400</v>
+        <v>1700</v>
       </c>
       <c r="G146" s="7"/>
       <c r="H146" s="8"/>
@@ -4742,19 +4667,19 @@
         <v>143</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>5400</v>
+        <v>1500</v>
       </c>
       <c r="G147" s="7"/>
       <c r="H147" s="8"/>
@@ -4767,24 +4692,24 @@
         <v>144</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="F148" s="6" t="n">
-        <v>5220</v>
+        <v>1500</v>
       </c>
       <c r="G148" s="7"/>
       <c r="H148" s="8"/>
       <c r="I148" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4792,24 +4717,24 @@
         <v>145</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>21</v>
+        <v>235</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D149" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>4800</v>
+        <v>1500</v>
       </c>
       <c r="G149" s="7"/>
       <c r="H149" s="8"/>
       <c r="I149" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4817,19 +4742,19 @@
         <v>146</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F150" s="6" t="n">
-        <v>4800</v>
+        <v>1400</v>
       </c>
       <c r="G150" s="7"/>
       <c r="H150" s="8"/>
@@ -4842,19 +4767,19 @@
         <v>147</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D151" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4400</v>
+        <v>1400</v>
       </c>
       <c r="G151" s="7"/>
       <c r="H151" s="8"/>
@@ -4867,19 +4792,19 @@
         <v>148</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="F152" s="6" t="n">
-        <v>4200</v>
+        <v>900</v>
       </c>
       <c r="G152" s="7"/>
       <c r="H152" s="8"/>
@@ -4888,587 +4813,12 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="5" t="n">
-        <v>149</v>
-      </c>
-      <c r="B153" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D153" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F153" s="6" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G153" s="7"/>
-      <c r="H153" s="8"/>
-      <c r="I153" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="B154" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D154" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E154" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F154" s="6" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G154" s="7"/>
-      <c r="H154" s="8"/>
-      <c r="I154" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="5" t="n">
-        <v>151</v>
-      </c>
-      <c r="B155" s="5" t="n">
-        <v>202</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D155" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E155" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F155" s="6" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G155" s="7"/>
-      <c r="H155" s="8"/>
-      <c r="I155" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="5" t="n">
-        <v>152</v>
-      </c>
-      <c r="B156" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D156" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E156" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F156" s="6" t="n">
-        <v>3900</v>
-      </c>
-      <c r="G156" s="7"/>
-      <c r="H156" s="8"/>
-      <c r="I156" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="5" t="n">
-        <v>153</v>
-      </c>
-      <c r="B157" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D157" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E157" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F157" s="6" t="n">
-        <v>3750</v>
-      </c>
-      <c r="G157" s="7"/>
-      <c r="H157" s="8"/>
-      <c r="I157" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="5" t="n">
-        <v>154</v>
-      </c>
-      <c r="B158" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D158" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F158" s="6" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G158" s="7"/>
-      <c r="H158" s="8"/>
-      <c r="I158" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="B159" s="5" t="n">
-        <v>218</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D159" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E159" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F159" s="6" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G159" s="7"/>
-      <c r="H159" s="8"/>
-      <c r="I159" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="5" t="n">
-        <v>156</v>
-      </c>
-      <c r="B160" s="5" t="n">
-        <v>133</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D160" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E160" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F160" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G160" s="7"/>
-      <c r="H160" s="8"/>
-      <c r="I160" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="5" t="n">
-        <v>157</v>
-      </c>
-      <c r="B161" s="5" t="n">
-        <v>158</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D161" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F161" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G161" s="7"/>
-      <c r="H161" s="8"/>
-      <c r="I161" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="5" t="n">
-        <v>158</v>
-      </c>
-      <c r="B162" s="5" t="n">
-        <v>217</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D162" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F162" s="6" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G162" s="7"/>
-      <c r="H162" s="8"/>
-      <c r="I162" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="B163" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D163" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E163" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F163" s="6" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G163" s="7"/>
-      <c r="H163" s="8"/>
-      <c r="I163" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="B164" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D164" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E164" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F164" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G164" s="7"/>
-      <c r="H164" s="8"/>
-      <c r="I164" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="5" t="n">
-        <v>161</v>
-      </c>
-      <c r="B165" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D165" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E165" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F165" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G165" s="7"/>
-      <c r="H165" s="8"/>
-      <c r="I165" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="5" t="n">
-        <v>162</v>
-      </c>
-      <c r="B166" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D166" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E166" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F166" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G166" s="7"/>
-      <c r="H166" s="8"/>
-      <c r="I166" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="5" t="n">
-        <v>163</v>
-      </c>
-      <c r="B167" s="5" t="n">
-        <v>216</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D167" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E167" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F167" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G167" s="7"/>
-      <c r="H167" s="8"/>
-      <c r="I167" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="5" t="n">
-        <v>164</v>
-      </c>
-      <c r="B168" s="5" t="n">
-        <v>220</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D168" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E168" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F168" s="6" t="n">
-        <v>1900</v>
-      </c>
-      <c r="G168" s="7"/>
-      <c r="H168" s="8"/>
-      <c r="I168" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="5" t="n">
-        <v>165</v>
-      </c>
-      <c r="B169" s="5" t="n">
-        <v>215</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D169" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E169" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F169" s="6" t="n">
-        <v>1700</v>
-      </c>
-      <c r="G169" s="7"/>
-      <c r="H169" s="8"/>
-      <c r="I169" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="5" t="n">
-        <v>166</v>
-      </c>
-      <c r="B170" s="5" t="n">
-        <v>214</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D170" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F170" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G170" s="7"/>
-      <c r="H170" s="8"/>
-      <c r="I170" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="B171" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D171" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F171" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G171" s="7"/>
-      <c r="H171" s="8"/>
-      <c r="I171" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="5" t="n">
-        <v>168</v>
-      </c>
-      <c r="B172" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D172" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E172" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F172" s="6" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G172" s="7"/>
-      <c r="H172" s="8"/>
-      <c r="I172" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="5" t="n">
-        <v>169</v>
-      </c>
-      <c r="B173" s="5" t="n">
-        <v>213</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D173" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E173" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F173" s="6" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G173" s="7"/>
-      <c r="H173" s="8"/>
-      <c r="I173" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="5" t="n">
-        <v>170</v>
-      </c>
-      <c r="B174" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D174" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F174" s="6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G174" s="7"/>
-      <c r="H174" s="8"/>
-      <c r="I174" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="5" t="n">
-        <v>171</v>
-      </c>
-      <c r="B175" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D175" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="F175" s="6" t="n">
-        <v>900</v>
-      </c>
-      <c r="G175" s="7"/>
-      <c r="H175" s="8"/>
-      <c r="I175" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E176" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="F176" s="10" t="n">
-        <f aca="false">SUM(F5:F175)</f>
-        <v>7047420</v>
+      <c r="E153" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F153" s="10" t="n">
+        <f aca="false">SUM(F5:F152)</f>
+        <v>5927959</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Rates_Needed_PR217_PR228.xlsx
+++ b/quotes/PR-217-228/Rates_Needed_PR217_PR228.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="190">
   <si>
     <t xml:space="preserve">Rates Needed - PR-217 &amp; PR-228 (unverified items, highest value first)</t>
   </si>
@@ -94,150 +94,153 @@
     <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
   </si>
   <si>
+    <t xml:space="preserve">BENCH VISE 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yato (heavy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS TOOL 16MMX16MMX200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS WELDING RODS 309L-16 2.6MM NO.12</t>
   </si>
   <si>
+    <t xml:space="preserve">Stainarc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHANICAL JACK 5 TON (Japan or Germany)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masada (Japan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC/DC SINGLE PHASE WELDING PLANT 300 AMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACTA20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRILL BIT 08 MM (Yato or any Good brand taiwan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS TOOL 12MMX12MMX200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHANICAL JACK 03 TONS (Japan or germany)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS PARTING OFF TOOL 1/8" X 3/4" X 8"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 3.25MM E6013 NO 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS WELDING RODS 316L-16 2.6MM NO.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS TOOL 10MMX10MMX200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 35MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRILL BIT 4MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS TOOL 08X08X200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 16MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer C-series HSS-Co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 2.5MM E6013, NO 10 Zodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 32MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 8MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAK 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCUMFERENCE TAPE (60-950) (D20-300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 10MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 2.5MM E7018 NO-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortrex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 6MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 18MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 5MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERNAL EXTRACTOR WITH REINFORCED COLLAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 19MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCUMFERENCE TAPE (940-2200) (D300-700)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIG WELDING TORCH AIR-COOLED 5METER</t>
+  </si>
+  <si>
     <t xml:space="preserve">Industrial</t>
   </si>
   <si>
-    <t xml:space="preserve">BENCH VISE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato (heavy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 16MMX16MMX200MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL JACK 5 TON (Japan or Germany)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masada (Japan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS WELDING RODS 316L-16 2.6MM NO.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC/DC SINGLE PHASE WELDING PLANT 300 AMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACTA20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRILL BIT 08 MM (Yato or any Good brand taiwan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 12MMX12MMX200MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL JACK 03 TONS (Japan or germany)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS PARTING OFF TOOL 1/8" X 3/4" X 8"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 3.25MM E6013 NO 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 10MMX10MMX200MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 35MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRILL BIT 4MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 08X08X200MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer C-series HSS-Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 2.5MM E6013, NO 10 Zodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 32MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 8MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAK 250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCUMFERENCE TAPE (60-950) (D20-300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 10MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 2.5MM E7018 NO-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortrex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 6MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 18MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 5MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERNAL EXTRACTOR WITH REINFORCED COLLAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 19MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCUMFERENCE TAPE (940-2200) (D300-700)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIG WELDING TORCH AIR-COOLED 5METER</t>
-  </si>
-  <si>
     <t xml:space="preserve">COTTON ROPE 2MM</t>
   </si>
   <si>
@@ -304,72 +307,72 @@
     <t xml:space="preserve">ANCHOR BOLT 12X160</t>
   </si>
   <si>
+    <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1-1/4" BSPF RIGHT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 14MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRINDER WHEEL SILICON CARBIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1/4" BSPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1/8" BSPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUEL GAS REGULATOR 0-2.5 BAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1" BSPF RIGHT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CUT PIECES OF CLOTHS FOR CLEANING</t>
   </si>
   <si>
-    <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1-1/4" BSPF RIGHT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 14MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL SILICON CARBIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/4" BSPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/8" BSPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUEL GAS REGULATOR 0-2.5 BAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1" BSPF RIGHT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
-  </si>
-  <si>
     <t xml:space="preserve">RED OXIDE POWDER</t>
   </si>
   <si>
@@ -533,9 +536,6 @@
   </si>
   <si>
     <t xml:space="preserve">GAS HOSE CONNECTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOILET CLEANING BRUSH</t>
   </si>
   <si>
     <t xml:space="preserve">NEEDLE FILE (5PCS SET)</t>
@@ -1033,7 +1033,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1192,19 +1192,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>167</v>
+        <v>224</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>240000</v>
+        <v>220000</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
@@ -1217,19 +1217,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>220000</v>
+        <v>192000</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="8"/>
@@ -1242,24 +1242,24 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>228</v>
+        <v>167</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>192000</v>
+        <v>176000</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
       <c r="I10" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1317,24 +1317,24 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>136000</v>
+        <v>126000</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="8"/>
       <c r="I13" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1342,24 +1342,24 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>122</v>
+        <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>126000</v>
+        <v>125000</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="8"/>
       <c r="I14" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1367,24 +1367,24 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>50</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>125000</v>
+        <v>118400</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="8"/>
       <c r="I15" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1392,24 +1392,24 @@
         <v>12</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>9</v>
+        <v>227</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>118400</v>
+        <v>115200</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="8"/>
       <c r="I16" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1417,19 +1417,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>227</v>
+        <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>115200</v>
+        <v>110000</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="8"/>
@@ -1442,19 +1442,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>5</v>
+        <v>229</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>41</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>110000</v>
+        <v>108000</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="8"/>
@@ -1467,24 +1467,24 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>108000</v>
+        <v>89920</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="8"/>
       <c r="I19" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1492,19 +1492,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>89920</v>
+        <v>88000</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="8"/>
@@ -1526,7 +1526,7 @@
         <v>24</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>86400</v>
@@ -1576,7 +1576,7 @@
         <v>50</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>65000</v>
@@ -1601,7 +1601,7 @@
         <v>24</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>62400</v>
@@ -1676,7 +1676,7 @@
         <v>40</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>58000</v>
@@ -2076,7 +2076,7 @@
         <v>2</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>40000</v>
@@ -2095,13 +2095,13 @@
         <v>145</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>500</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>40000</v>
@@ -2120,7 +2120,7 @@
         <v>81</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>2</v>
@@ -2145,13 +2145,13 @@
         <v>55</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>36000</v>
@@ -2170,13 +2170,13 @@
         <v>66</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>36000</v>
@@ -2195,13 +2195,13 @@
         <v>107</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>36000</v>
@@ -2220,13 +2220,13 @@
         <v>181</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>36000</v>
@@ -2245,7 +2245,7 @@
         <v>80</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>2</v>
@@ -2270,7 +2270,7 @@
         <v>84</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>1</v>
@@ -2295,7 +2295,7 @@
         <v>79</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>2</v>
@@ -2320,7 +2320,7 @@
         <v>212</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>1</v>
@@ -2345,7 +2345,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>2</v>
@@ -2370,13 +2370,13 @@
         <v>222</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>32000</v>
@@ -2395,13 +2395,13 @@
         <v>140</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>24</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>31200</v>
@@ -2420,7 +2420,7 @@
         <v>77</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>2</v>
@@ -2445,7 +2445,7 @@
         <v>49</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>1</v>
@@ -2470,13 +2470,13 @@
         <v>67</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>30000</v>
@@ -2495,7 +2495,7 @@
         <v>211</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>1</v>
@@ -2520,7 +2520,7 @@
         <v>76</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>2</v>
@@ -2545,13 +2545,13 @@
         <v>162</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>150</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>28500</v>
@@ -2567,19 +2567,19 @@
         <v>59</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="8"/>
@@ -2592,16 +2592,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>26000</v>
@@ -2617,19 +2617,19 @@
         <v>61</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>182</v>
+        <v>75</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>26000</v>
+        <v>25460</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="8"/>
@@ -2642,19 +2642,19 @@
         <v>62</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>25460</v>
+        <v>25000</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="8"/>
@@ -2667,19 +2667,19 @@
         <v>63</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="8"/>
@@ -2692,19 +2692,19 @@
         <v>64</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>24000</v>
+        <v>22500</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="8"/>
@@ -2717,24 +2717,24 @@
         <v>65</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>22500</v>
+        <v>22185</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="8"/>
       <c r="I69" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2742,24 +2742,24 @@
         <v>66</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>22185</v>
+        <v>21600</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="8"/>
       <c r="I70" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2767,19 +2767,19 @@
         <v>67</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>21600</v>
+        <v>21000</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="8"/>
@@ -2792,10 +2792,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>3</v>
@@ -2817,16 +2817,16 @@
         <v>69</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>21000</v>
@@ -2842,19 +2842,19 @@
         <v>70</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>21000</v>
+        <v>19200</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="8"/>
@@ -2867,24 +2867,24 @@
         <v>71</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D75" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>19200</v>
+        <v>18796</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="8"/>
       <c r="I75" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2892,24 +2892,24 @@
         <v>72</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>18796</v>
+        <v>18000</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="8"/>
       <c r="I76" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2917,16 +2917,16 @@
         <v>73</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>18000</v>
@@ -2942,16 +2942,16 @@
         <v>74</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>18000</v>
@@ -2967,19 +2967,19 @@
         <v>75</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
@@ -2992,16 +2992,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>16000</v>
@@ -3017,16 +3017,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>16000</v>
@@ -3034,7 +3034,7 @@
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
       <c r="I81" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3045,13 +3045,13 @@
         <v>154</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>12</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>15600</v>
@@ -3070,13 +3070,13 @@
         <v>109</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>15000</v>
@@ -3095,7 +3095,7 @@
         <v>28</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>3</v>
@@ -3120,7 +3120,7 @@
         <v>58</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>12</v>
@@ -3145,13 +3145,13 @@
         <v>139</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>24</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>14400</v>
@@ -3170,13 +3170,13 @@
         <v>187</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>14000</v>
@@ -3195,13 +3195,13 @@
         <v>130</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>13200</v>
@@ -3220,7 +3220,7 @@
         <v>56</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>1</v>
@@ -3251,7 +3251,7 @@
         <v>2</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>13000</v>
@@ -3270,13 +3270,13 @@
         <v>186</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D91" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>12900</v>
@@ -3295,7 +3295,7 @@
         <v>39</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D92" s="5" t="n">
         <v>3</v>
@@ -3320,13 +3320,13 @@
         <v>99</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D93" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>11000</v>
@@ -3345,13 +3345,13 @@
         <v>193</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D94" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>11000</v>
@@ -3370,13 +3370,13 @@
         <v>195</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D95" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>11000</v>
@@ -3395,13 +3395,13 @@
         <v>60</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D96" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10500</v>
@@ -3420,13 +3420,13 @@
         <v>185</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10500</v>
@@ -3445,13 +3445,13 @@
         <v>189</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10500</v>
@@ -3470,7 +3470,7 @@
         <v>62</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>3</v>
@@ -3501,7 +3501,7 @@
         <v>2</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10000</v>
@@ -3520,13 +3520,13 @@
         <v>160</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D101" s="5" t="n">
         <v>150</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>9750</v>
@@ -3545,13 +3545,13 @@
         <v>196</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>9600</v>
@@ -3570,7 +3570,7 @@
         <v>111</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>3</v>
@@ -3595,13 +3595,13 @@
         <v>100</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>9000</v>
@@ -3620,13 +3620,13 @@
         <v>188</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D105" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>8800</v>
@@ -3645,13 +3645,13 @@
         <v>184</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D106" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>8700</v>
@@ -3670,13 +3670,13 @@
         <v>1</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D107" s="5" t="n">
         <v>30</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>8400</v>
@@ -3695,13 +3695,13 @@
         <v>45</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D108" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>8000</v>
@@ -3720,13 +3720,13 @@
         <v>92</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D109" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>8000</v>
@@ -3745,13 +3745,13 @@
         <v>183</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D110" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>7500</v>
@@ -3770,13 +3770,13 @@
         <v>91</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D111" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>7000</v>
@@ -3795,13 +3795,13 @@
         <v>124</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D112" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>7000</v>
@@ -3820,13 +3820,13 @@
         <v>117</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D113" s="5" t="n">
         <v>15</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>6750</v>
@@ -3845,13 +3845,13 @@
         <v>118</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D114" s="5" t="n">
         <v>15</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>6750</v>
@@ -3870,7 +3870,7 @@
         <v>43</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D115" s="5" t="n">
         <v>4</v>
@@ -3895,13 +3895,13 @@
         <v>191</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D116" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>6400</v>
@@ -3920,7 +3920,7 @@
         <v>22</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>3</v>
@@ -3945,13 +3945,13 @@
         <v>36</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D118" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>6000</v>
@@ -3970,13 +3970,13 @@
         <v>126</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D119" s="5" t="n">
         <v>12</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>6000</v>
@@ -3995,13 +3995,13 @@
         <v>230</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D120" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>5950</v>
@@ -4020,13 +4020,13 @@
         <v>134</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D121" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>5400</v>
@@ -4045,13 +4045,13 @@
         <v>192</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D122" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>5400</v>
@@ -4070,13 +4070,13 @@
         <v>194</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D123" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>5400</v>
@@ -4095,13 +4095,13 @@
         <v>234</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D124" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>5220</v>
@@ -4120,7 +4120,7 @@
         <v>21</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>3</v>
@@ -4145,13 +4145,13 @@
         <v>125</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D126" s="5" t="n">
         <v>12</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>4800</v>
@@ -4170,13 +4170,13 @@
         <v>190</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D127" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>4400</v>
@@ -4195,13 +4195,13 @@
         <v>104</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D128" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>4000</v>
@@ -4220,13 +4220,13 @@
         <v>132</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D129" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>4000</v>
@@ -4245,13 +4245,13 @@
         <v>120</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D130" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>3900</v>
@@ -4270,7 +4270,7 @@
         <v>20</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D131" s="5" t="n">
         <v>3</v>
@@ -4295,13 +4295,13 @@
         <v>218</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D132" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>3600</v>
@@ -4320,13 +4320,13 @@
         <v>237</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D133" s="5" t="n">
         <v>24</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>3600</v>
@@ -4345,13 +4345,13 @@
         <v>133</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>3000</v>
@@ -4367,24 +4367,24 @@
         <v>131</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>3000</v>
+        <v>2704</v>
       </c>
       <c r="G135" s="7"/>
       <c r="H135" s="8"/>
       <c r="I135" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4392,24 +4392,24 @@
         <v>132</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D136" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="F136" s="6" t="n">
-        <v>2704</v>
+        <v>2600</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="8"/>
       <c r="I136" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4417,16 +4417,16 @@
         <v>133</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>2600</v>
@@ -4442,24 +4442,24 @@
         <v>134</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>2600</v>
+        <v>2580</v>
       </c>
       <c r="G138" s="7"/>
       <c r="H138" s="8"/>
       <c r="I138" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4467,10 +4467,10 @@
         <v>135</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D139" s="5" t="n">
         <v>3</v>
@@ -4479,7 +4479,7 @@
         <v>103</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2580</v>
+        <v>2382</v>
       </c>
       <c r="G139" s="7"/>
       <c r="H139" s="8"/>
@@ -4492,24 +4492,24 @@
         <v>136</v>
       </c>
       <c r="B140" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="C140" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C140" s="5" t="s">
-        <v>176</v>
-      </c>
       <c r="D140" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>2382</v>
+        <v>2100</v>
       </c>
       <c r="G140" s="7"/>
       <c r="H140" s="8"/>
       <c r="I140" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4517,16 +4517,16 @@
         <v>137</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D141" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>2100</v>
@@ -4542,16 +4542,16 @@
         <v>138</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D142" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>2100</v>
@@ -4567,16 +4567,16 @@
         <v>139</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>2100</v>
@@ -4592,19 +4592,19 @@
         <v>140</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="G144" s="7"/>
       <c r="H144" s="8"/>
@@ -4617,19 +4617,19 @@
         <v>141</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="8"/>
@@ -4642,19 +4642,19 @@
         <v>142</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D146" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F146" s="6" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="G146" s="7"/>
       <c r="H146" s="8"/>
@@ -4667,16 +4667,16 @@
         <v>143</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>1500</v>
@@ -4692,16 +4692,16 @@
         <v>144</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>1500</v>
@@ -4709,7 +4709,7 @@
       <c r="G148" s="7"/>
       <c r="H148" s="8"/>
       <c r="I148" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4717,24 +4717,24 @@
         <v>145</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>235</v>
+        <v>119</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="G149" s="7"/>
       <c r="H149" s="8"/>
       <c r="I149" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4742,16 +4742,16 @@
         <v>146</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>119</v>
+        <v>213</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D150" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>1400</v>
@@ -4767,19 +4767,19 @@
         <v>147</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>213</v>
+        <v>2</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D151" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="G151" s="7"/>
       <c r="H151" s="8"/>
@@ -4788,37 +4788,12 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="5" t="n">
-        <v>148</v>
-      </c>
-      <c r="B152" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D152" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E152" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F152" s="6" t="n">
-        <v>900</v>
-      </c>
-      <c r="G152" s="7"/>
-      <c r="H152" s="8"/>
-      <c r="I152" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E153" s="9" t="s">
+      <c r="E152" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F153" s="10" t="n">
-        <f aca="false">SUM(F5:F152)</f>
-        <v>5927959</v>
+      <c r="F152" s="10" t="n">
+        <f aca="false">SUM(F5:F151)</f>
+        <v>5800959</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Rates_Needed_PR217_PR228.xlsx
+++ b/quotes/PR-217-228/Rates_Needed_PR217_PR228.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="134">
   <si>
     <t xml:space="preserve">Rates Needed - PR-217 &amp; PR-228 (unverified items, highest value first)</t>
   </si>
@@ -73,91 +73,97 @@
     <t xml:space="preserve">WELDING CABLE 1000 AMPERE</t>
   </si>
   <si>
-    <t xml:space="preserve">Industrial (copper)</t>
+    <t xml:space="preserve">Industrial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec farq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDLESS DRILL DRIVER 150NM Bosch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosch Professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS TOOL 12MMX12MMX200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taiwan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS TOOL 16MMX16MMX200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila</t>
   </si>
   <si>
-    <t xml:space="preserve">CORDLESS DRILL DRIVER 150NM Bosch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosch Professional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spec farq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDLESS IMPACT WRENCH 350N (Bosch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
+    <t xml:space="preserve">HSS PARTING OFF TOOL 1/8" X 3/4" X 8"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS WELDING RODS 309L-16 2.6MM NO.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stainarc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS TOOL 10MMX10MMX200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC/DC SINGLE PHASE WELDING PLANT 300 AMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACTA20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED OXIDE POWDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 3.25MM E6013 NO 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS WELDING RODS 316L-16 2.6MM NO.12</t>
   </si>
   <si>
     <t xml:space="preserve">BENCH VISE 12"</t>
   </si>
   <si>
-    <t xml:space="preserve">Yato (heavy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 16MMX16MMX200MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS WELDING RODS 309L-16 2.6MM NO.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stainarc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL JACK 5 TON (Japan or Germany)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masada (Japan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC/DC SINGLE PHASE WELDING PLANT 300 AMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACTA20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRILL BIT 08 MM (Yato or any Good brand taiwan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 12MMX12MMX200MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL JACK 03 TONS (Japan or germany)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS PARTING OFF TOOL 1/8" X 3/4" X 8"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 3.25MM E6013 NO 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS WELDING RODS 316L-16 2.6MM NO.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 10MMX10MMX200MM</t>
+    <t xml:space="preserve">GRINDER WHEEL SILICON CARBIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 2.5MM E6013, NO 10 Zodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIG WELDING TORCH AIR-COOLED 5METER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET M18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 2.5MM E7018 NO-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortrex</t>
   </si>
   <si>
     <t xml:space="preserve">HSS DRILL BIT 35MM TAPER SHANK</t>
@@ -166,267 +172,153 @@
     <t xml:space="preserve">Dormer A130</t>
   </si>
   <si>
-    <t xml:space="preserve">DRILL BIT 4MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 08X08X200MM</t>
+    <t xml:space="preserve">COTTON ROPE 2MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR BOLT 12X160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL GREASE GUN 5KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C-CLAMP 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1-1/4" BSPF LEFT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVOLVING CENTRE MT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 18MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLIND RIVETS 04MMX25MM (1000PCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1-1/4" BSPF RIGHT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTSIDE CALIPER 20"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING HELMET (FLIP FRONT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSIDE CALIPER 20"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 16.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 3/8" BSPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 15.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harden</t>
   </si>
   <si>
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
   </si>
   <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer C-series HSS-Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 2.5MM E6013, NO 10 Zodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 32MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 8MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAK 250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCUMFERENCE TAPE (60-950) (D20-300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 10MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 2.5MM E7018 NO-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortrex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 6MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 18MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 5MM</t>
+    <t xml:space="preserve">TAP SET 1" BSPF RIGHT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 22MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUT PIECES OF CLOTHS FOR CLEANING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGNET SPIRIT LEVEL 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREASE PIPE 1/4"X12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUFFING DISC 125MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR GREASE GUN 500CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICE GRIP PLIER 08"</t>
   </si>
   <si>
     <t xml:space="preserve">INTERNAL EXTRACTOR WITH REINFORCED COLLAR</t>
   </si>
   <si>
-    <t xml:space="preserve">HSS DRILL BIT 19MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCUMFERENCE TAPE (940-2200) (D300-700)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIG WELDING TORCH AIR-COOLED 5METER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industrial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTTON ROPE 2MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 17.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUAL GREASE GUN 5KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVOLVING CENTRE MT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertex (Taiwan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-CLAMP 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1-1/4" BSPF LEFT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 17MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 25MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 16.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 25MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 16MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 JAW CHUCK 4"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRASS PLATED CUP WIRE BRUSH 125MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 15.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVOLVING CENTRE MT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 22MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 15MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANCHOR BOLT 12X160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1-1/4" BSPF RIGHT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 14MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL SILICON CARBIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/4" BSPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/8" BSPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUEL GAS REGULATOR 0-2.5 BAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1" BSPF RIGHT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUT PIECES OF CLOTHS FOR CLEANING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RED OXIDE POWDER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGNET SPIRIT LEVEL 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GREASE PIPE 1/4"X12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUFFING DISC 125MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUNGSTEN ELECTRODE 2.4MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIR GREASE GUN 500CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VICE GRIP PLIER 08"</t>
-  </si>
-  <si>
     <t xml:space="preserve">TAP SET 1/2" BSPF RIGHT HAND</t>
   </si>
   <si>
-    <t xml:space="preserve">INSIDE CALIPER 20"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic (Taiwan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OUTSIDE CALIPER 20"</t>
-  </si>
-  <si>
     <t xml:space="preserve">STEEL MEASURMENT TAPE 100M</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">TAP SET M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M20</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALIGNING PRY BAR DIA 5/8" X 18" LENGTH</t>
   </si>
   <si>
@@ -436,18 +328,9 @@
     <t xml:space="preserve">SMT</t>
   </si>
   <si>
-    <t xml:space="preserve">RACHET TAP HANDLE</t>
-  </si>
-  <si>
     <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 300MM</t>
   </si>
   <si>
-    <t xml:space="preserve">TAP SET 3/8" BSPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M18</t>
-  </si>
-  <si>
     <t xml:space="preserve">TAP SET M8</t>
   </si>
   <si>
@@ -460,106 +343,55 @@
     <t xml:space="preserve">ROUNDE FILE 12"</t>
   </si>
   <si>
-    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET M6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M2</t>
-  </si>
-  <si>
     <t xml:space="preserve">TORCH HEAD ARGON WELDING</t>
   </si>
   <si>
+    <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRAULIC JACK 3 TON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING ELCTRODE HOLDER 1000 AMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABLE LUGS 1000 AMPERE</t>
+  </si>
+  <si>
     <t xml:space="preserve">OXYGEN HOSE 08MM ID</t>
   </si>
   <si>
     <t xml:space="preserve">ACETYLENE GAS HOSE 08 ID</t>
   </si>
   <si>
-    <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLLECT BODY FOR ARGON 2.4MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDRAULIC JACK 3 TON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHORT SLEEVE TIG WELDING GLOVES 10-INCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSIDE CALIPER 06"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OUTSIDE CALIPER 06"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING ELCTRODE HOLDER 1000 AMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLLECT OF ARGON 2.4MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING HELMET (FLIP FRONT)</t>
+    <t xml:space="preserve">NEEDLE FILE (5PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT SIZE 12MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIE NUT HANDLE LARGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERAMIC CUP NO.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERAMIC CUP NO.7</t>
   </si>
   <si>
     <t xml:space="preserve">ARGON GAS HOSE 06MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIP CLEANER FOR GAS WELDING TORCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN HEX KEY 12MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT SIZE 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABLE LUGS 1000 AMPERE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAS HOSE CONNECTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEEDLE FILE (5PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT SIZE 12MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT HANDLE LARGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 150MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLIND RIVETS 04MMX25MM (1000PCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERAMIC CUP NO.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERAMIC CUP NO.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERAMIC CUP NO.7</t>
   </si>
   <si>
     <t xml:space="preserve">DIE NUT SIZE 10MM</t>
@@ -1033,7 +865,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I152"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1129,7 +961,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>640000</v>
+        <v>721800</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="8"/>
@@ -1159,7 +991,7 @@
       <c r="G6" s="7"/>
       <c r="H6" s="8"/>
       <c r="I6" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1167,19 +999,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>41</v>
+        <v>227</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F7" s="6" t="n">
-        <v>300000</v>
+        <v>279624</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="8"/>
@@ -1192,24 +1024,24 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>220000</v>
+        <v>192000</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
       <c r="I8" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1217,7 +1049,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>26</v>
@@ -1226,10 +1058,10 @@
         <v>24</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>192000</v>
+        <v>181656</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="8"/>
@@ -1245,13 +1077,13 @@
         <v>167</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>40</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>176000</v>
@@ -1259,7 +1091,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
       <c r="I10" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1267,24 +1099,24 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="8"/>
       <c r="I11" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1292,19 +1124,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>74</v>
+        <v>226</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>140000</v>
+        <v>128904</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="8"/>
@@ -1320,13 +1152,13 @@
         <v>122</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>126000</v>
@@ -1334,7 +1166,7 @@
       <c r="G13" s="7"/>
       <c r="H13" s="8"/>
       <c r="I13" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1342,19 +1174,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>125000</v>
+        <v>122040</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="8"/>
@@ -1370,7 +1202,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>4</v>
@@ -1384,7 +1216,7 @@
       <c r="G15" s="7"/>
       <c r="H15" s="8"/>
       <c r="I15" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1392,19 +1224,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>227</v>
+        <v>165</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>115200</v>
+        <v>89920</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="8"/>
@@ -1417,19 +1249,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>110000</v>
+        <v>88000</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="8"/>
@@ -1442,19 +1274,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>108000</v>
+        <v>79200</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="8"/>
@@ -1467,24 +1299,24 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>89920</v>
+        <v>62598</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="8"/>
       <c r="I19" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1492,24 +1324,24 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>88000</v>
+        <v>58000</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="8"/>
       <c r="I20" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1517,19 +1349,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>226</v>
+        <v>96</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>86400</v>
+        <v>55838</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -1542,19 +1374,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>68210</v>
+        <v>50104</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="8"/>
@@ -1567,19 +1399,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>65000</v>
+        <v>46782</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="8"/>
@@ -1592,19 +1424,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>225</v>
+        <v>166</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>62400</v>
+        <v>46500</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
@@ -1617,19 +1449,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>60000</v>
+        <v>40500</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="8"/>
@@ -1642,24 +1474,24 @@
         <v>22</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>209</v>
+        <v>145</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="F26" s="6" t="n">
-        <v>59970</v>
+        <v>40000</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="8"/>
       <c r="I26" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1667,24 +1499,24 @@
         <v>23</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>58000</v>
+        <v>39900</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="8"/>
       <c r="I27" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1692,19 +1524,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>57270</v>
+        <v>39900</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
@@ -1717,19 +1549,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>54060</v>
+        <v>39640</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="8"/>
@@ -1742,24 +1574,24 @@
         <v>26</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>52000</v>
+        <v>36000</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="8"/>
       <c r="I30" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1767,24 +1599,24 @@
         <v>27</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>50000</v>
+        <v>36000</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="8"/>
       <c r="I31" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1792,24 +1624,24 @@
         <v>28</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>49980</v>
+        <v>36000</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="8"/>
       <c r="I32" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1817,19 +1649,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>46560</v>
+        <v>34988</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="8"/>
@@ -1842,24 +1674,24 @@
         <v>30</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>46500</v>
+        <v>33328</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
       <c r="I34" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1867,19 +1699,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>46500</v>
+        <v>31019</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="8"/>
@@ -1892,19 +1724,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>45780</v>
+        <v>30376</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -1917,19 +1749,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>204</v>
+        <v>89</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>42780</v>
+        <v>29714</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -1942,19 +1774,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>42000</v>
+        <v>28080</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
@@ -1967,24 +1799,24 @@
         <v>35</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>41980</v>
+        <v>26000</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1992,24 +1824,24 @@
         <v>36</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>40000</v>
+        <v>26000</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2017,19 +1849,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>40000</v>
+        <v>25576</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
@@ -2042,19 +1874,19 @@
         <v>38</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>40000</v>
+        <v>25108</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
@@ -2067,19 +1899,19 @@
         <v>39</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>40000</v>
+        <v>23896</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
@@ -2092,19 +1924,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>40000</v>
+        <v>22500</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
@@ -2117,19 +1949,19 @@
         <v>41</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>37020</v>
+        <v>22185</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
@@ -2142,19 +1974,19 @@
         <v>42</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>36000</v>
+        <v>21735</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="8"/>
@@ -2167,24 +1999,24 @@
         <v>43</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>36000</v>
+        <v>21600</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="8"/>
       <c r="I47" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2192,19 +2024,19 @@
         <v>44</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>36000</v>
+        <v>19686</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="8"/>
@@ -2217,19 +2049,19 @@
         <v>45</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>36000</v>
+        <v>19260</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="8"/>
@@ -2242,24 +2074,24 @@
         <v>46</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>35360</v>
+        <v>19200</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="8"/>
       <c r="I50" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2267,19 +2099,19 @@
         <v>47</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>34430</v>
+        <v>18796</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="8"/>
@@ -2292,19 +2124,19 @@
         <v>48</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>33720</v>
+        <v>18765</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="8"/>
@@ -2317,24 +2149,24 @@
         <v>49</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>33400</v>
+        <v>18000</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="8"/>
       <c r="I53" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2342,19 +2174,19 @@
         <v>50</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>32060</v>
+        <v>16870</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="8"/>
@@ -2367,24 +2199,24 @@
         <v>51</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>222</v>
+        <v>98</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="8"/>
       <c r="I55" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2392,19 +2224,19 @@
         <v>52</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>31200</v>
+        <v>16000</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="8"/>
@@ -2417,24 +2249,24 @@
         <v>53</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>30420</v>
+        <v>15000</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="8"/>
       <c r="I57" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2442,24 +2274,24 @@
         <v>54</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>30000</v>
+        <v>14400</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="8"/>
       <c r="I58" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2467,24 +2299,24 @@
         <v>55</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>30000</v>
+        <v>14400</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="8"/>
       <c r="I59" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2492,24 +2324,24 @@
         <v>56</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>28830</v>
+        <v>14400</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="8"/>
       <c r="I60" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2517,19 +2349,19 @@
         <v>57</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>28760</v>
+        <v>14040</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="8"/>
@@ -2542,19 +2374,19 @@
         <v>58</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>28500</v>
+        <v>14040</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="8"/>
@@ -2567,19 +2399,19 @@
         <v>59</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>26000</v>
+        <v>13500</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="8"/>
@@ -2592,24 +2424,24 @@
         <v>60</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>26000</v>
+        <v>13000</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="8"/>
       <c r="I64" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2617,19 +2449,19 @@
         <v>61</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>25460</v>
+        <v>12526</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="8"/>
@@ -2642,19 +2474,19 @@
         <v>62</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>25000</v>
+        <v>12000</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="8"/>
@@ -2667,19 +2499,19 @@
         <v>63</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>24000</v>
+        <v>11340</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="8"/>
@@ -2692,24 +2524,24 @@
         <v>64</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>22500</v>
+        <v>11000</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="8"/>
       <c r="I68" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2717,24 +2549,24 @@
         <v>65</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>22185</v>
+        <v>10500</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="8"/>
       <c r="I69" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2742,19 +2574,19 @@
         <v>66</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>21600</v>
+        <v>10497</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="8"/>
@@ -2767,19 +2599,19 @@
         <v>67</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>21000</v>
+        <v>9750</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="8"/>
@@ -2792,19 +2624,19 @@
         <v>68</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>21000</v>
+        <v>9375</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="8"/>
@@ -2817,24 +2649,24 @@
         <v>69</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>21000</v>
+        <v>8700</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="8"/>
       <c r="I73" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2842,19 +2674,19 @@
         <v>70</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>19200</v>
+        <v>8400</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="8"/>
@@ -2867,24 +2699,24 @@
         <v>71</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D75" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>18796</v>
+        <v>8000</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="8"/>
       <c r="I75" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2892,24 +2724,24 @@
         <v>72</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="8"/>
       <c r="I76" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2917,19 +2749,19 @@
         <v>73</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="D77" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>18000</v>
+        <v>6578</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="8"/>
@@ -2942,24 +2774,24 @@
         <v>74</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>18000</v>
+        <v>6400</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="8"/>
       <c r="I78" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2967,24 +2799,24 @@
         <v>75</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>16000</v>
+        <v>6000</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
       <c r="I79" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2992,19 +2824,19 @@
         <v>76</v>
       </c>
       <c r="B80" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="F80" s="6" t="n">
-        <v>16000</v>
+        <v>6000</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
@@ -3017,24 +2849,24 @@
         <v>77</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>16000</v>
+        <v>5950</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
       <c r="I81" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3042,19 +2874,19 @@
         <v>78</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>15600</v>
+        <v>5220</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="8"/>
@@ -3067,24 +2899,24 @@
         <v>79</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>15000</v>
+        <v>4800</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="8"/>
       <c r="I83" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3092,19 +2924,19 @@
         <v>80</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>28</v>
+        <v>237</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>14400</v>
+        <v>3600</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="8"/>
@@ -3117,19 +2949,19 @@
         <v>81</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>14400</v>
+        <v>3240</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="8"/>
@@ -3142,19 +2974,19 @@
         <v>82</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>14400</v>
+        <v>3240</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="8"/>
@@ -3167,19 +2999,19 @@
         <v>83</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>14000</v>
+        <v>2704</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="8"/>
@@ -3192,24 +3024,24 @@
         <v>84</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>130</v>
+        <v>217</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>13200</v>
+        <v>2600</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="8"/>
       <c r="I88" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3217,24 +3049,24 @@
         <v>85</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>56</v>
+        <v>221</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>13000</v>
+        <v>2600</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="8"/>
       <c r="I89" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3242,19 +3074,19 @@
         <v>86</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>13000</v>
+        <v>2382</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -3267,19 +3099,19 @@
         <v>87</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>186</v>
+        <v>129</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>12900</v>
+        <v>2382</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -3292,24 +3124,24 @@
         <v>88</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>12000</v>
+        <v>2160</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
       <c r="I92" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3317,24 +3149,24 @@
         <v>89</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>11000</v>
+        <v>2100</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
       <c r="I93" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3342,24 +3174,24 @@
         <v>90</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>11000</v>
+        <v>1900</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="8"/>
       <c r="I94" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3367,24 +3199,24 @@
         <v>91</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D95" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>11000</v>
+        <v>1700</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="8"/>
       <c r="I95" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3392,24 +3224,24 @@
         <v>92</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D96" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>10500</v>
+        <v>1500</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="8"/>
       <c r="I96" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3417,24 +3249,24 @@
         <v>93</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>10500</v>
+        <v>1500</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="8"/>
       <c r="I97" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3442,19 +3274,19 @@
         <v>94</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>189</v>
+        <v>235</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>10500</v>
+        <v>1500</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="8"/>
@@ -3467,24 +3299,24 @@
         <v>95</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>10497</v>
+        <v>1400</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="8"/>
       <c r="I99" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3492,24 +3324,24 @@
         <v>96</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>88</v>
+        <v>213</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D100" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>10000</v>
+        <v>1400</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="8"/>
       <c r="I100" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3517,1283 +3349,33 @@
         <v>97</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>9750</v>
+        <v>612</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="8"/>
       <c r="I101" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="B102" s="5" t="n">
-        <v>196</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D102" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F102" s="6" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G102" s="7"/>
-      <c r="H102" s="8"/>
-      <c r="I102" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="B103" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D103" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F103" s="6" t="n">
-        <v>9375</v>
-      </c>
-      <c r="G103" s="7"/>
-      <c r="H103" s="8"/>
-      <c r="I103" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="B104" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D104" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F104" s="6" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G104" s="7"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="B105" s="5" t="n">
-        <v>188</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D105" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>8800</v>
-      </c>
-      <c r="G105" s="7"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="B106" s="5" t="n">
-        <v>184</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D106" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F106" s="6" t="n">
-        <v>8700</v>
-      </c>
-      <c r="G106" s="7"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="5" t="n">
-        <v>103</v>
-      </c>
-      <c r="B107" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D107" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F107" s="6" t="n">
-        <v>8400</v>
-      </c>
-      <c r="G107" s="7"/>
-      <c r="H107" s="8"/>
-      <c r="I107" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="B108" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D108" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F108" s="6" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G108" s="7"/>
-      <c r="H108" s="8"/>
-      <c r="I108" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="5" t="n">
-        <v>105</v>
-      </c>
-      <c r="B109" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D109" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F109" s="6" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G109" s="7"/>
-      <c r="H109" s="8"/>
-      <c r="I109" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="B110" s="5" t="n">
-        <v>183</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D110" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F110" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="G110" s="7"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="B111" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D111" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F111" s="6" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G111" s="7"/>
-      <c r="H111" s="8"/>
-      <c r="I111" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="B112" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D112" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F112" s="6" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G112" s="7"/>
-      <c r="H112" s="8"/>
-      <c r="I112" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="B113" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D113" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F113" s="6" t="n">
-        <v>6750</v>
-      </c>
-      <c r="G113" s="7"/>
-      <c r="H113" s="8"/>
-      <c r="I113" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="B114" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D114" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F114" s="6" t="n">
-        <v>6750</v>
-      </c>
-      <c r="G114" s="7"/>
-      <c r="H114" s="8"/>
-      <c r="I114" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="B115" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D115" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F115" s="6" t="n">
-        <v>6400</v>
-      </c>
-      <c r="G115" s="7"/>
-      <c r="H115" s="8"/>
-      <c r="I115" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="5" t="n">
-        <v>112</v>
-      </c>
-      <c r="B116" s="5" t="n">
-        <v>191</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D116" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F116" s="6" t="n">
-        <v>6400</v>
-      </c>
-      <c r="G116" s="7"/>
-      <c r="H116" s="8"/>
-      <c r="I116" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="B117" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D117" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F117" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G117" s="7"/>
-      <c r="H117" s="8"/>
-      <c r="I117" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="B118" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D118" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F118" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G118" s="7"/>
-      <c r="H118" s="8"/>
-      <c r="I118" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="5" t="n">
-        <v>115</v>
-      </c>
-      <c r="B119" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D119" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F119" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G119" s="7"/>
-      <c r="H119" s="8"/>
-      <c r="I119" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="B120" s="5" t="n">
-        <v>230</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D120" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F120" s="6" t="n">
-        <v>5950</v>
-      </c>
-      <c r="G120" s="7"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="B121" s="5" t="n">
-        <v>134</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D121" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F121" s="6" t="n">
-        <v>5400</v>
-      </c>
-      <c r="G121" s="7"/>
-      <c r="H121" s="8"/>
-      <c r="I121" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="B122" s="5" t="n">
-        <v>192</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D122" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F122" s="6" t="n">
-        <v>5400</v>
-      </c>
-      <c r="G122" s="7"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="B123" s="5" t="n">
-        <v>194</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D123" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F123" s="6" t="n">
-        <v>5400</v>
-      </c>
-      <c r="G123" s="7"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="B124" s="5" t="n">
-        <v>234</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D124" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F124" s="6" t="n">
-        <v>5220</v>
-      </c>
-      <c r="G124" s="7"/>
-      <c r="H124" s="8"/>
-      <c r="I124" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="B125" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D125" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F125" s="6" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G125" s="7"/>
-      <c r="H125" s="8"/>
-      <c r="I125" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="B126" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D126" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F126" s="6" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G126" s="7"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="B127" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D127" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F127" s="6" t="n">
-        <v>4400</v>
-      </c>
-      <c r="G127" s="7"/>
-      <c r="H127" s="8"/>
-      <c r="I127" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="B128" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D128" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F128" s="6" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G128" s="7"/>
-      <c r="H128" s="8"/>
-      <c r="I128" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="B129" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D129" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F129" s="6" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G129" s="7"/>
-      <c r="H129" s="8"/>
-      <c r="I129" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="B130" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D130" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F130" s="6" t="n">
-        <v>3900</v>
-      </c>
-      <c r="G130" s="7"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="B131" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D131" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F131" s="6" t="n">
-        <v>3750</v>
-      </c>
-      <c r="G131" s="7"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="B132" s="5" t="n">
-        <v>218</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D132" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F132" s="6" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G132" s="7"/>
-      <c r="H132" s="8"/>
-      <c r="I132" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="B133" s="5" t="n">
-        <v>237</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D133" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F133" s="6" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G133" s="7"/>
-      <c r="H133" s="8"/>
-      <c r="I133" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="B134" s="5" t="n">
+      <c r="E102" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D134" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F134" s="6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G134" s="7"/>
-      <c r="H134" s="8"/>
-      <c r="I134" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="B135" s="5" t="n">
-        <v>202</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D135" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F135" s="6" t="n">
-        <v>2704</v>
-      </c>
-      <c r="G135" s="7"/>
-      <c r="H135" s="8"/>
-      <c r="I135" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="B136" s="5" t="n">
-        <v>217</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D136" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F136" s="6" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G136" s="7"/>
-      <c r="H136" s="8"/>
-      <c r="I136" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="5" t="n">
-        <v>133</v>
-      </c>
-      <c r="B137" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D137" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F137" s="6" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G137" s="7"/>
-      <c r="H137" s="8"/>
-      <c r="I137" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="5" t="n">
-        <v>134</v>
-      </c>
-      <c r="B138" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D138" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E138" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F138" s="6" t="n">
-        <v>2580</v>
-      </c>
-      <c r="G138" s="7"/>
-      <c r="H138" s="8"/>
-      <c r="I138" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="5" t="n">
-        <v>135</v>
-      </c>
-      <c r="B139" s="5" t="n">
-        <v>177</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D139" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F139" s="6" t="n">
-        <v>2382</v>
-      </c>
-      <c r="G139" s="7"/>
-      <c r="H139" s="8"/>
-      <c r="I139" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="5" t="n">
-        <v>136</v>
-      </c>
-      <c r="B140" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D140" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F140" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G140" s="7"/>
-      <c r="H140" s="8"/>
-      <c r="I140" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="5" t="n">
-        <v>137</v>
-      </c>
-      <c r="B141" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D141" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F141" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G141" s="7"/>
-      <c r="H141" s="8"/>
-      <c r="I141" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="5" t="n">
-        <v>138</v>
-      </c>
-      <c r="B142" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D142" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F142" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G142" s="7"/>
-      <c r="H142" s="8"/>
-      <c r="I142" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="5" t="n">
-        <v>139</v>
-      </c>
-      <c r="B143" s="5" t="n">
-        <v>216</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D143" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F143" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G143" s="7"/>
-      <c r="H143" s="8"/>
-      <c r="I143" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="B144" s="5" t="n">
-        <v>220</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D144" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F144" s="6" t="n">
-        <v>1900</v>
-      </c>
-      <c r="G144" s="7"/>
-      <c r="H144" s="8"/>
-      <c r="I144" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="5" t="n">
-        <v>141</v>
-      </c>
-      <c r="B145" s="5" t="n">
-        <v>215</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D145" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F145" s="6" t="n">
-        <v>1700</v>
-      </c>
-      <c r="G145" s="7"/>
-      <c r="H145" s="8"/>
-      <c r="I145" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="B146" s="5" t="n">
-        <v>214</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D146" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F146" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G146" s="7"/>
-      <c r="H146" s="8"/>
-      <c r="I146" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="B147" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D147" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F147" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G147" s="7"/>
-      <c r="H147" s="8"/>
-      <c r="I147" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="5" t="n">
-        <v>144</v>
-      </c>
-      <c r="B148" s="5" t="n">
-        <v>235</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D148" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F148" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G148" s="7"/>
-      <c r="H148" s="8"/>
-      <c r="I148" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="B149" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D149" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F149" s="6" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G149" s="7"/>
-      <c r="H149" s="8"/>
-      <c r="I149" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="B150" s="5" t="n">
-        <v>213</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D150" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F150" s="6" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G150" s="7"/>
-      <c r="H150" s="8"/>
-      <c r="I150" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="5" t="n">
-        <v>147</v>
-      </c>
-      <c r="B151" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D151" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E151" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F151" s="6" t="n">
-        <v>900</v>
-      </c>
-      <c r="G151" s="7"/>
-      <c r="H151" s="8"/>
-      <c r="I151" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E152" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="F152" s="10" t="n">
-        <f aca="false">SUM(F5:F151)</f>
-        <v>5800959</v>
+      <c r="F102" s="10" t="n">
+        <f aca="false">SUM(F5:F101)</f>
+        <v>4346324</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Rates_Needed_PR217_PR228.xlsx
+++ b/quotes/PR-217-228/Rates_Needed_PR217_PR228.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="114">
   <si>
     <t xml:space="preserve">Rates Needed - PR-217 &amp; PR-228 (unverified items, highest value first)</t>
   </si>
@@ -91,69 +91,75 @@
     <t xml:space="preserve">Taiwan</t>
   </si>
   <si>
+    <t xml:space="preserve">HSS PARTING OFF TOOL 1/8" X 3/4" X 8"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1-1/4" BSPF LEFT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1-1/4" BSPF RIGHT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS WELDING RODS 309L-16 2.6MM NO.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stainarc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL GREASE GUN 5KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS TOOL 10MMX10MMX200MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC/DC SINGLE PHASE WELDING PLANT 300 AMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACTA20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED OXIDE POWDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 3.25MM E6013 NO 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS WELDING RODS 316L-16 2.6MM NO.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENCH VISE 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRINDER WHEEL SILICON CARBIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING RODS 2.5MM E6013, NO 10 Zodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREASE PIPE 1/4"X12"</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS TOOL 16MMX16MMX200MM</t>
   </si>
   <si>
-    <t xml:space="preserve">Dormer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS PARTING OFF TOOL 1/8" X 3/4" X 8"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS WELDING RODS 309L-16 2.6MM NO.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stainarc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS TOOL 10MMX10MMX200MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC/DC SINGLE PHASE WELDING PLANT 300 AMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACTA20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RED OXIDE POWDER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 3.25MM E6013 NO 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS WELDING RODS 316L-16 2.6MM NO.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BENCH VISE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRINDER WHEEL SILICON CARBIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING RODS 2.5MM E6013, NO 10 Zodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insize</t>
-  </si>
-  <si>
     <t xml:space="preserve">TIG WELDING TORCH AIR-COOLED 5METER</t>
   </si>
   <si>
@@ -172,123 +178,93 @@
     <t xml:space="preserve">Dormer A130</t>
   </si>
   <si>
-    <t xml:space="preserve">COTTON ROPE 2MM</t>
+    <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR BOLT 12X160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVOLVING CENTRE MT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 18MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLIND RIVETS 04MMX25MM (1000PCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTSIDE CALIPER 20"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELDING HELMET (FLIP FRONT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSIDE CALIPER 20"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 16.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SET 3/8" BSPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR GREASE GUN 500CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 15.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">END MILL CUTTER SIZE 22MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUT PIECES OF CLOTHS FOR CLEANING</t>
   </si>
   <si>
     <t xml:space="preserve">Local</t>
   </si>
   <si>
-    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANCHOR BOLT 12X160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUAL GREASE GUN 5KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-CLAMP 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1-1/4" BSPF LEFT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVOLVING CENTRE MT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 18MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLIND RIVETS 04MMX25MM (1000PCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1-1/4" BSPF RIGHT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OUTSIDE CALIPER 20"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WELDING HELMET (FLIP FRONT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSIDE CALIPER 20"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 16.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 3/8" BSPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 15.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1" BSPF RIGHT HAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END MILL CUTTER SIZE 22MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUT PIECES OF CLOTHS FOR CLEANING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGNET SPIRIT LEVEL 12"</t>
-  </si>
-  <si>
     <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
   </si>
   <si>
-    <t xml:space="preserve">GREASE PIPE 1/4"X12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUFFING DISC 125MM</t>
-  </si>
-  <si>
     <t xml:space="preserve">GRINDER WHEEL ALUMINIUM OXIDE GRIT 24</t>
   </si>
   <si>
@@ -298,9 +274,6 @@
     <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
   </si>
   <si>
-    <t xml:space="preserve">AIR GREASE GUN 500CC</t>
-  </si>
-  <si>
     <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M2</t>
   </si>
   <si>
@@ -310,9 +283,6 @@
     <t xml:space="preserve">INTERNAL EXTRACTOR WITH REINFORCED COLLAR</t>
   </si>
   <si>
-    <t xml:space="preserve">TAP SET 1/2" BSPF RIGHT HAND</t>
-  </si>
-  <si>
     <t xml:space="preserve">STEEL MEASURMENT TAPE 100M</t>
   </si>
   <si>
@@ -322,6 +292,9 @@
     <t xml:space="preserve">ALIGNING PRY BAR DIA 5/8" X 18" LENGTH</t>
   </si>
   <si>
+    <t xml:space="preserve">DIE NUT SIZE 12MM</t>
+  </si>
+  <si>
     <t xml:space="preserve">ANCHOR BOLT 10X110</t>
   </si>
   <si>
@@ -331,40 +304,28 @@
     <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 300MM</t>
   </si>
   <si>
-    <t xml:space="preserve">TAP SET M8</t>
-  </si>
-  <si>
     <t xml:space="preserve">STONE CUTTING DISC 4"</t>
   </si>
   <si>
     <t xml:space="preserve">Rhodius</t>
   </si>
   <si>
-    <t xml:space="preserve">ROUNDE FILE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORCH HEAD ARGON WELDING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
+    <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDRAULIC JACK 3 TON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronix</t>
   </si>
   <si>
     <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
   </si>
   <si>
-    <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDRAULIC JACK 3 TON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronix</t>
-  </si>
-  <si>
     <t xml:space="preserve">WELDING ELCTRODE HOLDER 1000 AMP</t>
   </si>
   <si>
-    <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
+    <t xml:space="preserve">DIE NUT HANDLE MEDIUM</t>
   </si>
   <si>
     <t xml:space="preserve">CABLE LUGS 1000 AMPERE</t>
@@ -379,12 +340,6 @@
     <t xml:space="preserve">NEEDLE FILE (5PCS SET)</t>
   </si>
   <si>
-    <t xml:space="preserve">DIE NUT SIZE 12MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT HANDLE LARGE</t>
-  </si>
-  <si>
     <t xml:space="preserve">CERAMIC CUP NO.6</t>
   </si>
   <si>
@@ -394,28 +349,13 @@
     <t xml:space="preserve">ARGON GAS HOSE 06MM</t>
   </si>
   <si>
-    <t xml:space="preserve">DIE NUT SIZE 10MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT HANDLE MEDIUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT SIZE 8MM</t>
+    <t xml:space="preserve">DIE NUT HANDLE SMALL</t>
   </si>
   <si>
     <t xml:space="preserve">DIE NUT SIZE 6MM</t>
   </si>
   <si>
-    <t xml:space="preserve">DIE NUT HANDLE SMALL</t>
-  </si>
-  <si>
     <t xml:space="preserve">EARTH CLAMP 1000 AMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYLINDER KEY/SPANNER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIE NUT SIZE 5MM</t>
   </si>
   <si>
     <t xml:space="preserve">STEEL NAIL 1-1/2" Taiwan</t>
@@ -865,7 +805,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1024,7 +964,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>23</v>
@@ -1033,15 +973,15 @@
         <v>24</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>192000</v>
+        <v>181656</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
       <c r="I8" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1049,19 +989,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>181656</v>
+        <v>179788</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="8"/>
@@ -1074,19 +1014,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>176000</v>
+        <v>179788</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
@@ -1099,24 +1039,24 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>140000</v>
+        <v>176000</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="8"/>
       <c r="I11" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1124,19 +1064,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>226</v>
+        <v>55</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>128904</v>
+        <v>134000</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="8"/>
@@ -1149,19 +1089,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>122</v>
+        <v>226</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>126000</v>
+        <v>128904</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="8"/>
@@ -1174,19 +1114,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>122040</v>
+        <v>126000</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="8"/>
@@ -1199,19 +1139,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>118400</v>
+        <v>122040</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="8"/>
@@ -1224,19 +1164,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>165</v>
+        <v>9</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>89920</v>
+        <v>118400</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="8"/>
@@ -1249,19 +1189,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>88000</v>
+        <v>93911</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="8"/>
@@ -1274,19 +1214,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>79200</v>
+        <v>89920</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="8"/>
@@ -1299,19 +1239,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>62598</v>
+        <v>88000</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="8"/>
@@ -1324,19 +1264,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>58000</v>
+        <v>79200</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="8"/>
@@ -1349,19 +1289,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>55838</v>
+        <v>62598</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
@@ -1374,19 +1314,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>50104</v>
+        <v>58000</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="8"/>
@@ -1399,19 +1339,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>46782</v>
+        <v>55838</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="8"/>
@@ -1424,19 +1364,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>46500</v>
+        <v>54996</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
@@ -1449,19 +1389,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>87</v>
+        <v>228</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>40500</v>
+        <v>50112</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="8"/>
@@ -1474,24 +1414,24 @@
         <v>22</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>40000</v>
+        <v>50104</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="8"/>
       <c r="I26" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1499,19 +1439,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>39900</v>
+        <v>46782</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="8"/>
@@ -1524,19 +1464,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>39900</v>
+        <v>46500</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
@@ -1549,19 +1489,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>39640</v>
+        <v>40500</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="8"/>
@@ -1574,24 +1514,24 @@
         <v>26</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>36000</v>
+        <v>40172</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="8"/>
       <c r="I30" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1599,24 +1539,24 @@
         <v>27</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>36000</v>
+        <v>39900</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="8"/>
       <c r="I31" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1624,24 +1564,24 @@
         <v>28</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>36000</v>
+        <v>39900</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="8"/>
       <c r="I32" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1649,19 +1589,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>34988</v>
+        <v>39640</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="8"/>
@@ -1674,19 +1614,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>210</v>
+        <v>66</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>33328</v>
+        <v>34988</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
@@ -1699,19 +1639,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>31019</v>
+        <v>33328</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="8"/>
@@ -1724,19 +1664,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>30376</v>
+        <v>31019</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -1749,10 +1689,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>2</v>
@@ -1761,7 +1701,7 @@
         <v>22</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>29714</v>
+        <v>30376</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -1774,19 +1714,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>28080</v>
+        <v>29714</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
@@ -1799,24 +1739,24 @@
         <v>35</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>26000</v>
+        <v>28080</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1824,24 +1764,24 @@
         <v>36</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>26000</v>
+        <v>25576</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1849,19 +1789,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>195</v>
+        <v>27</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>25576</v>
+        <v>25472</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
@@ -1877,7 +1817,7 @@
         <v>104</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>4</v>
@@ -1902,7 +1842,7 @@
         <v>193</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>2</v>
@@ -1927,13 +1867,13 @@
         <v>79</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>22500</v>
@@ -1952,13 +1892,13 @@
         <v>73</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>22185</v>
@@ -1977,13 +1917,13 @@
         <v>100</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>21735</v>
@@ -1999,24 +1939,24 @@
         <v>43</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>21600</v>
+        <v>20921</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="8"/>
       <c r="I47" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2027,7 +1967,7 @@
         <v>49</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>1</v>
@@ -2052,13 +1992,13 @@
         <v>77</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>19260</v>
@@ -2074,24 +2014,24 @@
         <v>46</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>19200</v>
+        <v>18796</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="8"/>
       <c r="I50" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2099,19 +2039,19 @@
         <v>47</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>18796</v>
+        <v>18765</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="8"/>
@@ -2124,19 +2064,19 @@
         <v>48</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>47</v>
+        <v>211</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>18765</v>
+        <v>16870</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="8"/>
@@ -2149,24 +2089,24 @@
         <v>49</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="8"/>
       <c r="I53" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2174,19 +2114,19 @@
         <v>50</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>211</v>
+        <v>28</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>16870</v>
+        <v>14988</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="8"/>
@@ -2199,24 +2139,24 @@
         <v>51</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>16000</v>
+        <v>14040</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="8"/>
       <c r="I55" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2224,19 +2164,19 @@
         <v>52</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>16000</v>
+        <v>14040</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="8"/>
@@ -2249,24 +2189,24 @@
         <v>53</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>15000</v>
+        <v>13500</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="8"/>
       <c r="I57" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2274,24 +2214,24 @@
         <v>54</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>14400</v>
+        <v>12526</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="8"/>
       <c r="I58" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2299,24 +2239,24 @@
         <v>55</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="8"/>
       <c r="I59" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2324,24 +2264,24 @@
         <v>56</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>14400</v>
+        <v>11340</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="8"/>
       <c r="I60" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2349,19 +2289,19 @@
         <v>57</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>142</v>
+        <v>60</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>14040</v>
+        <v>10500</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="8"/>
@@ -2374,19 +2314,19 @@
         <v>58</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>14040</v>
+        <v>10497</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="8"/>
@@ -2399,19 +2339,19 @@
         <v>59</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>13500</v>
+        <v>10286</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="8"/>
@@ -2424,24 +2364,24 @@
         <v>60</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="C64" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>4</v>
-      </c>
       <c r="F64" s="6" t="n">
-        <v>13000</v>
+        <v>9750</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="8"/>
       <c r="I64" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2449,19 +2389,19 @@
         <v>61</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>93</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>12526</v>
+        <v>9375</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="8"/>
@@ -2474,19 +2414,19 @@
         <v>62</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>12000</v>
+        <v>8400</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="8"/>
@@ -2499,19 +2439,19 @@
         <v>63</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>11340</v>
+        <v>6578</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="8"/>
@@ -2524,24 +2464,24 @@
         <v>64</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>96</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="8"/>
       <c r="I68" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2549,19 +2489,19 @@
         <v>65</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>97</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>98</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>10500</v>
+        <v>5950</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="8"/>
@@ -2574,7 +2514,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>99</v>
@@ -2583,10 +2523,10 @@
         <v>3</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>10497</v>
+        <v>5535</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="8"/>
@@ -2599,19 +2539,19 @@
         <v>67</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>100</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>9750</v>
+        <v>5220</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="8"/>
@@ -2624,19 +2564,19 @@
         <v>68</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>111</v>
+        <v>220</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>9375</v>
+        <v>3728</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="8"/>
@@ -2649,24 +2589,24 @@
         <v>69</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>8700</v>
+        <v>3600</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="8"/>
       <c r="I73" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2674,19 +2614,19 @@
         <v>70</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>8400</v>
+        <v>3240</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="8"/>
@@ -2699,24 +2639,24 @@
         <v>71</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>8000</v>
+        <v>3240</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="8"/>
       <c r="I75" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2724,24 +2664,24 @@
         <v>72</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D76" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>7000</v>
+        <v>2704</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="8"/>
       <c r="I76" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2749,19 +2689,19 @@
         <v>73</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>6578</v>
+        <v>2382</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="8"/>
@@ -2774,24 +2714,24 @@
         <v>74</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>6400</v>
+        <v>2382</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="8"/>
       <c r="I78" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2799,24 +2739,24 @@
         <v>75</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>6000</v>
+        <v>2160</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
       <c r="I79" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2824,19 +2764,19 @@
         <v>76</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>36</v>
+        <v>219</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>6000</v>
+        <v>2037</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
@@ -2849,19 +2789,19 @@
         <v>77</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>5950</v>
+        <v>1626</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
@@ -2874,19 +2814,19 @@
         <v>78</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>5220</v>
+        <v>1500</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="8"/>
@@ -2899,483 +2839,33 @@
         <v>79</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>4800</v>
+        <v>612</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="8"/>
       <c r="I83" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="B84" s="5" t="n">
-        <v>237</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D84" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F84" s="6" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G84" s="7"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="B85" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D85" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F85" s="6" t="n">
-        <v>3240</v>
-      </c>
-      <c r="G85" s="7"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="B86" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D86" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F86" s="6" t="n">
-        <v>3240</v>
-      </c>
-      <c r="G86" s="7"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="B87" s="5" t="n">
-        <v>202</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D87" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F87" s="6" t="n">
-        <v>2704</v>
-      </c>
-      <c r="G87" s="7"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="B88" s="5" t="n">
-        <v>217</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D88" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F88" s="6" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G88" s="7"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="B89" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D89" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F89" s="6" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G89" s="7"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="B90" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D90" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F90" s="6" t="n">
-        <v>2382</v>
-      </c>
-      <c r="G90" s="7"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="B91" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D91" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F91" s="6" t="n">
-        <v>2382</v>
-      </c>
-      <c r="G91" s="7"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="B92" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D92" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>2160</v>
-      </c>
-      <c r="G92" s="7"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="B93" s="5" t="n">
-        <v>216</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="G93" s="7"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="B94" s="5" t="n">
-        <v>220</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F94" s="6" t="n">
-        <v>1900</v>
-      </c>
-      <c r="G94" s="7"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="B95" s="5" t="n">
-        <v>215</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F95" s="6" t="n">
-        <v>1700</v>
-      </c>
-      <c r="G95" s="7"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="B96" s="5" t="n">
-        <v>214</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D96" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F96" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G96" s="7"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G97" s="7"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="B98" s="5" t="n">
-        <v>235</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D98" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F98" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G98" s="7"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="B99" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D99" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G99" s="7"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="B100" s="5" t="n">
-        <v>213</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D100" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G100" s="7"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="5" t="n">
-        <v>97</v>
-      </c>
-      <c r="B101" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D101" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>612</v>
-      </c>
-      <c r="G101" s="7"/>
-      <c r="H101" s="8"/>
-      <c r="I101" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E102" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F102" s="10" t="n">
-        <f aca="false">SUM(F5:F101)</f>
-        <v>4346324</v>
+      <c r="E84" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <f aca="false">SUM(F5:F83)</f>
+        <v>4417084</v>
       </c>
     </row>
   </sheetData>
